--- a/input/excel_templates/BM-08_09.xlsx
+++ b/input/excel_templates/BM-08_09.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vqpf3-my.sharepoint.com/personal/cuongnguyen239_vqpf3_onmicrosoft_com/Documents/KETOAN_TAICHINH/10_CONG BO BAN HANH/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vqpf3-my.sharepoint.com/personal/cuongnguyen239_vqpf3_onmicrosoft_com/Documents/KETOAN_TAICHINH/FINANCIAL_SYSTEM/input/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_DD47577602485B72DF81880EF49F17801691E63C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{385A8E3A-9878-476C-B6B5-8DCC650A1D2D}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_DD47577602485B72DF81880EF49F17801691E63C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7997F2DD-6BA7-4F11-8794-FD584901F329}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BM-08 Tổng hợp CP-Khóa hạng" sheetId="1" r:id="rId1"/>
-    <sheet name="BM-09 Chi phí dở dang TK154" sheetId="2" r:id="rId2"/>
+    <sheet name="BM08" sheetId="1" r:id="rId1"/>
+    <sheet name="BM09" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -635,93 +635,93 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1009,808 +1009,845 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="3" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8" t="s">
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8" t="s">
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="1:14" ht="9.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
     </row>
     <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
     </row>
     <row r="11" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11" t="s">
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12" t="s">
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="N12" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="16">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6">
         <f t="shared" ref="M13:M20" si="0">SUM(C13:L13)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="14"/>
+      <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="16">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N14" s="14"/>
+      <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="16">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="4"/>
     </row>
     <row r="16" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="16">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N16" s="14"/>
+      <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="16">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N17" s="14"/>
+      <c r="N17" s="4"/>
     </row>
     <row r="18" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="16">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N18" s="14"/>
+      <c r="N18" s="4"/>
     </row>
     <row r="19" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="16">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N19" s="14"/>
+      <c r="N19" s="4"/>
     </row>
     <row r="20" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="16">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N20" s="14"/>
+      <c r="N20" s="4"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18">
+      <c r="B21" s="23"/>
+      <c r="C21" s="7">
         <f t="shared" ref="C21:M21" si="1">SUM(C13:C20)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N21" s="19"/>
+      <c r="N21" s="8"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
     </row>
     <row r="24" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23">
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12">
         <f>D25-E25</f>
         <v>0</v>
       </c>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23">
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12">
         <f>D26-E26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23">
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12">
         <f>D27-E27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
     </row>
     <row r="28" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="20"/>
-      <c r="B28" s="25" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="18">
+      <c r="C28" s="11"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="7">
         <f>D28-E28</f>
         <v>0</v>
       </c>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3" t="s">
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3" t="s">
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
     </row>
     <row r="33" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4" t="s">
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
     </row>
     <row r="34" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4" t="s">
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
     </row>
     <row r="35" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
     </row>
     <row r="36" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="G25:N25"/>
+    <mergeCell ref="G26:N26"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="G28:N28"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:N32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:N33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="J34:N34"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="G35:I35"/>
@@ -1819,43 +1856,6 @@
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="J36:N36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:N33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="J34:N34"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="A30:N30"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:N32"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="G26:N26"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:N6"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.19685039370078741" top="0.19685039370078741" bottom="0.11811023622047245" header="0.11811023622047245" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1905,1134 +1905,1189 @@
       <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="26"/>
+      <c r="I6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="26"/>
+      <c r="I7" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
     </row>
     <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
     </row>
     <row r="13" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15" t="str">
+      <c r="A14" s="14"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="str">
         <f t="shared" ref="G14:G23" si="0">IF(E14&gt;0,E14-F14,"")</f>
         <v/>
       </c>
-      <c r="H14" s="27" t="str">
+      <c r="H14" s="15" t="str">
         <f t="shared" ref="H14:H23" si="1">IF(E14&gt;0,F14/E14,"")</f>
         <v/>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K14" s="14"/>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="26"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15" t="str">
+      <c r="A15" s="14"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H15" s="27" t="str">
+      <c r="H15" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J15" s="26" t="s">
+      <c r="J15" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K15" s="14"/>
+      <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15" t="str">
+      <c r="A16" s="14"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H16" s="27" t="str">
+      <c r="H16" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J16" s="26" t="s">
+      <c r="J16" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K16" s="14"/>
+      <c r="K16" s="4"/>
     </row>
     <row r="17" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="26"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15" t="str">
+      <c r="A17" s="14"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H17" s="27" t="str">
+      <c r="H17" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J17" s="26" t="s">
+      <c r="J17" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K17" s="14"/>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="26"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15" t="str">
+      <c r="A18" s="14"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H18" s="27" t="str">
+      <c r="H18" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J18" s="26" t="s">
+      <c r="J18" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K18" s="14"/>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="26"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15" t="str">
+      <c r="A19" s="14"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H19" s="27" t="str">
+      <c r="H19" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J19" s="26" t="s">
+      <c r="J19" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="14"/>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="26"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15" t="str">
+      <c r="A20" s="14"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H20" s="27" t="str">
+      <c r="H20" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="26" t="s">
+      <c r="J20" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="14"/>
+      <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="26"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15" t="str">
+      <c r="A21" s="14"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H21" s="27" t="str">
+      <c r="H21" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I21" s="28" t="s">
+      <c r="I21" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="26" t="s">
+      <c r="J21" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K21" s="14"/>
+      <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="26"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15" t="str">
+      <c r="A22" s="14"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H22" s="27" t="str">
+      <c r="H22" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I22" s="28" t="s">
+      <c r="I22" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="26" t="s">
+      <c r="J22" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K22" s="14"/>
+      <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="26"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15" t="str">
+      <c r="A23" s="14"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H23" s="27" t="str">
+      <c r="H23" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="I23" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J23" s="26" t="s">
+      <c r="J23" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="K23" s="14"/>
+      <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18">
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="7">
         <f>SUM(E14:E23)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="7">
         <f>SUM(F14:F23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="7">
         <f>SUM(G14:G23)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
     </row>
     <row r="26" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
     </row>
     <row r="28" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G28" s="20" t="s">
+      <c r="G28" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I28" s="20" t="s">
+      <c r="I28" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J28" s="20" t="s">
+      <c r="J28" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="26"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16" t="str">
+      <c r="A29" s="14"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6" t="str">
         <f t="shared" ref="F29:F38" si="2">IF(C29+D29-E29&lt;&gt;0,C29+D29-E29,"")</f>
         <v/>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="26" t="str">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="14" t="str">
         <f t="shared" ref="J29:J38" si="3">IF(F29=C29+D29-E29,"✓ OK","⚠ Sai")</f>
         <v>⚠ Sai</v>
       </c>
-      <c r="K29" s="14"/>
+      <c r="K29" s="4"/>
     </row>
     <row r="30" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="26"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16" t="str">
+      <c r="A30" s="14"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="26" t="str">
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K30" s="14"/>
+      <c r="K30" s="4"/>
     </row>
     <row r="31" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="26"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16" t="str">
+      <c r="A31" s="14"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="26" t="str">
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K31" s="14"/>
+      <c r="K31" s="4"/>
     </row>
     <row r="32" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="26"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16" t="str">
+      <c r="A32" s="14"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="26" t="str">
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K32" s="14"/>
+      <c r="K32" s="4"/>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="26"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16" t="str">
+      <c r="A33" s="14"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="26" t="str">
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K33" s="14"/>
+      <c r="K33" s="4"/>
     </row>
     <row r="34" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="26"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16" t="str">
+      <c r="A34" s="14"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="26" t="str">
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K34" s="14"/>
+      <c r="K34" s="4"/>
     </row>
     <row r="35" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="26"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16" t="str">
+      <c r="A35" s="14"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="26" t="str">
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K35" s="14"/>
+      <c r="K35" s="4"/>
     </row>
     <row r="36" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="26"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16" t="str">
+      <c r="A36" s="14"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="26" t="str">
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K36" s="14"/>
+      <c r="K36" s="4"/>
     </row>
     <row r="37" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="26"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="16" t="str">
+      <c r="A37" s="14"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="26" t="str">
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K37" s="14"/>
+      <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="26"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16" t="str">
+      <c r="A38" s="14"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="26" t="str">
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="14" t="str">
         <f t="shared" si="3"/>
         <v>⚠ Sai</v>
       </c>
-      <c r="K38" s="14"/>
+      <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18">
+      <c r="B39" s="23"/>
+      <c r="C39" s="7">
         <f t="shared" ref="C39:I39" si="4">SUM(C29:C38)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
     </row>
     <row r="41" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
     </row>
     <row r="42" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
     </row>
     <row r="43" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="28" t="s">
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
     </row>
     <row r="44" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="28" t="s">
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
     </row>
     <row r="45" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="28" t="s">
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J45" s="24"/>
-      <c r="K45" s="24"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
     </row>
     <row r="46" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="31" t="s">
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
     </row>
     <row r="47" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="28" t="s">
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
     </row>
     <row r="48" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="31" t="s">
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
     </row>
     <row r="51" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
     </row>
     <row r="52" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
     </row>
     <row r="53" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="27"/>
     </row>
     <row r="54" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8" t="s">
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="27"/>
+      <c r="K54" s="27"/>
     </row>
     <row r="55" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="27"/>
+      <c r="K55" s="27"/>
     </row>
     <row r="56" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8" t="s">
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="27"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
     </row>
     <row r="59" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3" t="s">
+      <c r="B59" s="22"/>
+      <c r="C59" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3" t="s">
+      <c r="D59" s="22"/>
+      <c r="E59" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3" t="s">
+      <c r="F59" s="22"/>
+      <c r="G59" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
     </row>
     <row r="60" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4" t="s">
+      <c r="B60" s="19"/>
+      <c r="C60" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4" t="s">
+      <c r="D60" s="19"/>
+      <c r="E60" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4" t="s">
+      <c r="F60" s="19"/>
+      <c r="G60" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
     </row>
     <row r="61" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4" t="s">
+      <c r="B61" s="19"/>
+      <c r="C61" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="s">
+      <c r="D61" s="19"/>
+      <c r="E61" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4" t="s">
+      <c r="F61" s="19"/>
+      <c r="G61" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
     </row>
     <row r="62" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
+      <c r="A62" s="19"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
     </row>
     <row r="63" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="67">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:K53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="D54:K54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="D55:K55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="D56:K56"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:K59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:K60"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="E63:F63"/>
@@ -3045,61 +3100,6 @@
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="G62:K62"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="G59:K59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G60:K60"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="D54:K54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D55:K55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="D56:K56"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A52:K52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D53:K53"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.39370078740157483" top="0.39370078740157483" bottom="0.31496062992125984" header="0.31496062992125984" footer="0.31496062992125984"/>
